--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488304_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488304_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9587</v>
+        <v>4.1157</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4771</v>
+        <v>2.7758</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4816</v>
+        <v>1.34</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1443</v>
+        <v>4.3022</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6295</v>
+        <v>5.7183</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5147</v>
+        <v>-1.4162</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6005</v>
+        <v>4.2314</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4641</v>
+        <v>5.402</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1364</v>
+        <v>-1.1706</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4562</v>
+        <v>0.0707</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1655</v>
+        <v>0.3163</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6217</v>
+        <v>-0.2456</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R2" t="n">
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5877</v>
+        <v>0.443</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0112</v>
+        <v>-0.0469</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5989</v>
+        <v>0.4899</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6997</v>
+        <v>-0.6294</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0005</v>
+        <v>0.6294</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6992</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5407</v>
+        <v>3.6676</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5454</v>
+        <v>2.4568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9953</v>
+        <v>1.2108</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3022</v>
+        <v>3.1443</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7183</v>
+        <v>1.6295</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4162</v>
+        <v>1.5147</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2314</v>
+        <v>3.6005</v>
       </c>
       <c r="K3" t="n">
-        <v>5.402</v>
+        <v>1.4641</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1706</v>
+        <v>2.1364</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0707</v>
+        <v>-0.4562</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3163</v>
+        <v>0.1655</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2456</v>
+        <v>-0.6217</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R3" t="n">
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1321</v>
+        <v>1.2967</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2773</v>
+        <v>-0.0314</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1452</v>
+        <v>1.3281</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6294</v>
+        <v>-1.6997</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6294</v>
+        <v>-0.0005</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>-1.6992</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7601</v>
+        <v>2.9745</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7134</v>
+        <v>1.9704</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0467</v>
+        <v>1.004</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4648</v>
+        <v>2.8867</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8317</v>
+        <v>0.6041</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3669</v>
+        <v>2.2826</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3826</v>
+        <v>2.5687</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8897</v>
+        <v>-0.159</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5071</v>
+        <v>2.7277</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0.3181</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.058</v>
+        <v>0.7632</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8598</v>
+        <v>-0.4451</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5509</v>
+        <v>0.7346</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4452</v>
+        <v>-0.1159</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9961</v>
+        <v>0.8505</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0703</v>
+        <v>-1.5733</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6289</v>
+        <v>0.6294</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6992</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6887</v>
+        <v>2.486</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1525</v>
+        <v>2.0302</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5362</v>
+        <v>0.4558</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8867</v>
+        <v>2.4648</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6041</v>
+        <v>3.8317</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2826</v>
+        <v>-1.3669</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5687</v>
+        <v>3.3826</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.159</v>
+        <v>3.8897</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7277</v>
+        <v>-0.5071</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3181</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7632</v>
+        <v>-0.058</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4451</v>
+        <v>-0.8598</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0382</v>
+        <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5511</v>
+        <v>1.2768</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9339</v>
+        <v>-0.1284</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3827</v>
+        <v>1.4052</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5733</v>
+        <v>-1.0703</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6294</v>
+        <v>0.6289</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2027</v>
+        <v>-1.6992</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8327</v>
+        <v>0.7494</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0111</v>
+        <v>-1.4462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8438</v>
+        <v>2.1956</v>
       </c>
       <c r="G7" t="n">
-        <v>3.423</v>
+        <v>-0.8962</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2418</v>
+        <v>-0.4249</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1811</v>
+        <v>-0.4714</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8741</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.618</v>
+        <v>-0.4046</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2561</v>
+        <v>-0.487</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4511</v>
+        <v>-0.0047</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6239</v>
+        <v>-0.0203</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.075</v>
+        <v>0.0156</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
         <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0038</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3209</v>
+        <v>-0.2571</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6829</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6294</v>
+        <v>1.133</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.315</v>
+        <v>0.6289</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3144</v>
+        <v>0.5041</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2914</v>
+        <v>0.6046</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9041</v>
+        <v>-0.1407</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1956</v>
+        <v>0.7453</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8962</v>
+        <v>3.423</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4249</v>
+        <v>1.2418</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4714</v>
+        <v>2.1811</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8915999999999999</v>
+        <v>3.8741</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4046</v>
+        <v>0.618</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.487</v>
+        <v>3.2561</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0047</v>
+        <v>-0.4511</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0203</v>
+        <v>0.6239</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0156</v>
+        <v>-1.075</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.9646</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-3.891</v>
       </c>
       <c r="R8" t="n">
         <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0547</v>
+        <v>0.7756</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.715</v>
+        <v>0.1912</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.5844</v>
       </c>
       <c r="V8" t="n">
-        <v>1.133</v>
+        <v>-0.6294</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6289</v>
+        <v>-0.315</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5041</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. POL RUBIO</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8874</v>
+        <v>-1.2647</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7434</v>
+        <v>-2.394</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.144</v>
+        <v>1.1293</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0211</v>
+        <v>-1.0638</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0464</v>
+        <v>0.0284</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0676</v>
+        <v>-1.0922</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6529</v>
+        <v>-1.5106</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6529</v>
+        <v>-1.8756</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3683</v>
+        <v>0.4469</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0464</v>
+        <v>-0.3366</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4147</v>
+        <v>0.7834</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0602</v>
+        <v>-0.1862</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1641</v>
+        <v>-0.2534</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2243</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.7559</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>D. POL RUBIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9196</v>
+        <v>-1.9613</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8519</v>
+        <v>-1.7434</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9323</v>
+        <v>-0.2178</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0638</v>
+        <v>-1.0211</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0284</v>
+        <v>0.0464</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0922</v>
+        <v>-1.0676</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5106</v>
+        <v>-0.6529</v>
       </c>
       <c r="K10" t="n">
-        <v>0.365</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8756</v>
+        <v>-0.6529</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4469</v>
+        <v>-0.3683</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3366</v>
+        <v>0.0464</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7834</v>
+        <v>-0.4147</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7411</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8411</v>
+        <v>-0.0137</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7113</v>
+        <v>-0.1641</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1298</v>
+        <v>0.1505</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7559</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2325</v>
+        <v>-1.9628</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6887</v>
+        <v>-1.4929</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5438</v>
+        <v>-0.4699</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6423</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4643</v>
+        <v>-0.1946</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.383</v>
+        <v>-0.1871</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0813</v>
+        <v>-0.0075</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1259</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6673</v>
+        <v>-3.1284</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8312</v>
+        <v>-7.2431</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1639</v>
+        <v>4.1147</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3544</v>
@@ -1390,13 +1390,13 @@
         <v>2.594</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0578</v>
+        <v>0.5966</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2114</v>
+        <v>-0.2005</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7971</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.931700000000002</v>
+        <v>7.846800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.575800000000001</v>
+        <v>-3.6609</v>
       </c>
       <c r="F13" t="n">
-        <v>11.5076</v>
+        <v>11.5078</v>
       </c>
       <c r="G13" t="n">
-        <v>9.8094</v>
+        <v>9.809399999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>8.080299999999998</v>
+        <v>8.080300000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.728499999999999</v>
+        <v>1.7285</v>
       </c>
       <c r="J13" t="n">
         <v>10.7847</v>
       </c>
       <c r="K13" t="n">
-        <v>6.6005</v>
+        <v>6.600499999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>4.184099999999999</v>
+        <v>4.1841</v>
       </c>
       <c r="M13" t="n">
         <v>-0.9753999999999998</v>
@@ -1468,13 +1468,13 @@
         <v>12.9701</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3265</v>
+        <v>5.241399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1087</v>
+        <v>-1.1936</v>
       </c>
       <c r="U13" t="n">
-        <v>6.435</v>
+        <v>6.435000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-5.350899999999999</v>
@@ -1483,7 +1483,7 @@
         <v>1.5711</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.922099999999999</v>
+        <v>-6.9221</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.8178</v>
+        <v>9.4983</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7645</v>
+        <v>7.6665</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0533</v>
+        <v>1.8317</v>
       </c>
       <c r="G14" t="n">
         <v>4.405</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0594</v>
+        <v>-0.379</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9923</v>
+        <v>-1.0902</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9329</v>
+        <v>0.7113</v>
       </c>
       <c r="V14" t="n">
         <v>5.287</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2774</v>
+        <v>-0.181</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.3084</v>
+        <v>-1.8332</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0309</v>
+        <v>1.6523</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6697</v>
+        <v>-1.1468</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3596</v>
+        <v>-1.2372</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6898</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.0311</v>
+        <v>0.268</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.114</v>
+        <v>-0.4596</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0829</v>
+        <v>0.7276</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3613</v>
+        <v>-1.4148</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7544</v>
+        <v>-0.7775</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6069</v>
+        <v>-0.6373</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8252</v>
+        <v>-0.6389</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6491</v>
+        <v>-1.1748</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1761</v>
+        <v>0.5359</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0623</v>
+        <v>-0.0629</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0623</v>
+        <v>-0.0629</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>N. RAMIREZ PRIETO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4062</v>
+        <v>-0.4076</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4006</v>
+        <v>-0.2901</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8068</v>
+        <v>-0.1175</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0518</v>
+        <v>-0.4234</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8032</v>
+        <v>-0.4834</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2487</v>
+        <v>0.0599</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1044</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0382</v>
+        <v>0.0215</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0415</v>
+        <v>0.0829</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1315</v>
+        <v>-0.5278</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8414</v>
+        <v>-0.5048</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2901</v>
+        <v>-0.023</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0336</v>
+        <v>-0.54</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3209</v>
+        <v>-0.3945</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7128</v>
+        <v>-0.1455</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. RAMIREZ PRIETO</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5547</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.388</v>
+        <v>0.7538</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1667</v>
+        <v>-1.4751</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4234</v>
+        <v>-0.3863</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4834</v>
+        <v>-1.3352</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0599</v>
+        <v>0.9489</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1044</v>
+        <v>2.8009</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0215</v>
+        <v>0.777</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0829</v>
+        <v>2.0239</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5278</v>
+        <v>-3.1872</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5048</v>
+        <v>-2.1122</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.023</v>
+        <v>-1.075</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6872</v>
+        <v>-0.8167</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4924</v>
+        <v>-1.1201</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1947</v>
+        <v>0.3034</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0142</v>
+        <v>-0.9943</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5187</v>
+        <v>-0.0891</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5045</v>
+        <v>-0.9053</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1468</v>
+        <v>-2.0518</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2372</v>
+        <v>-0.8032</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09030000000000001</v>
+        <v>-1.2487</v>
       </c>
       <c r="J19" t="n">
-        <v>0.268</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4596</v>
+        <v>0.0382</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7276</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4148</v>
+        <v>-2.1315</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7775</v>
+        <v>-0.8414</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6373</v>
+        <v>-1.2901</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.594</v>
+        <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4721</v>
+        <v>0.4455</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.8603</v>
+        <v>-0.1688</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3882</v>
+        <v>0.6143</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0629</v>
+        <v>-0.3144</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0629</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8746</v>
+        <v>-1.6031</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0683</v>
+        <v>-3.9939</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9429</v>
+        <v>2.3908</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3863</v>
+        <v>-1.6697</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3352</v>
+        <v>-2.3596</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9489</v>
+        <v>0.6898</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8009</v>
+        <v>-3.0311</v>
       </c>
       <c r="K20" t="n">
-        <v>0.777</v>
+        <v>-3.114</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0239</v>
+        <v>0.0829</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1872</v>
+        <v>1.3613</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1122</v>
+        <v>0.7544</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.075</v>
+        <v>0.6069</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1117</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.97</v>
+        <v>0.4996</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8056</v>
+        <v>-0.0364</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1644</v>
+        <v>0.5359</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.63</v>
+        <v>-0.0623</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6294</v>
+        <v>-0.0623</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7191</v>
+        <v>-2.8669</v>
       </c>
       <c r="E21" t="n">
         <v>-2.9899</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2708</v>
+        <v>0.1231</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3555</v>
@@ -2092,13 +2092,13 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3261</v>
+        <v>-0.4738</v>
       </c>
       <c r="T21" t="n">
         <v>-0.5471</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2211</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0.63</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6913</v>
+        <v>-4.3166</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.3581</v>
+        <v>-5.5279</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6668</v>
+        <v>1.2114</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9493</v>
+        <v>-5.8534</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6651</v>
+        <v>-3.1545</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6143</v>
+        <v>-2.6989</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4397</v>
+        <v>-4.3402</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7985</v>
+        <v>-2.0404</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2382</v>
+        <v>-2.2998</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5095</v>
+        <v>-1.5132</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1334</v>
+        <v>-1.1141</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3761</v>
+        <v>-0.3991</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0382</v>
+        <v>2.9646</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3636</v>
+        <v>-0.7893</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8792</v>
+        <v>-0.9261</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5155</v>
+        <v>0.1368</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6373</v>
+        <v>2.1409</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.26</v>
+        <v>2.5177</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3773</v>
+        <v>-0.3768</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8342</v>
+        <v>-4.9616</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.43</v>
+        <v>-6.4561</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5958</v>
+        <v>1.4945</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.8534</v>
+        <v>-1.9493</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1545</v>
+        <v>0.6651</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6989</v>
+        <v>-2.6143</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.3402</v>
+        <v>-1.4397</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.0404</v>
+        <v>0.7985</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2998</v>
+        <v>-2.2382</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5132</v>
+        <v>-0.5095</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1141</v>
+        <v>-0.1334</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3991</v>
+        <v>-0.3761</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1853</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R23" t="n">
-        <v>2.9646</v>
+        <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3069</v>
+        <v>-0.6339</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8282</v>
+        <v>-0.9771</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4788</v>
+        <v>0.3432</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1409</v>
+        <v>-1.6373</v>
       </c>
       <c r="W23" t="n">
-        <v>2.5177</v>
+        <v>-1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3768</v>
+        <v>-0.3773</v>
       </c>
     </row>
     <row r="24">
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.931800000000001</v>
+        <v>-5.931999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.1376</v>
+        <v>-12.1378</v>
       </c>
       <c r="F24" t="n">
-        <v>6.205699999999999</v>
+        <v>6.2059</v>
       </c>
       <c r="G24" t="n">
         <v>-9.809100000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.0806</v>
+        <v>-8.080599999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-1.7287</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9753999999999978</v>
+        <v>0.9753999999999989</v>
       </c>
       <c r="K24" t="n">
         <v>-1.48</v>
       </c>
       <c r="L24" t="n">
-        <v>2.455499999999999</v>
+        <v>2.4555</v>
       </c>
       <c r="M24" t="n">
         <v>-10.7845</v>
@@ -2335,7 +2335,7 @@
         <v>3.1087</v>
       </c>
       <c r="V24" t="n">
-        <v>5.350999999999999</v>
+        <v>5.351000000000001</v>
       </c>
       <c r="W24" t="n">
         <v>6.292100000000001</v>
